--- a/data/Survival/07232025.xlsx
+++ b/data/Survival/07232025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/graceleuchtenberger/Library/Mobile Documents/com~apple~CloudDocs/Documents/Density_field/data/Survival/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{830E9F00-0904-164E-BE77-D4A12E964A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D0DDD6-F2E9-D24F-B615-06EE28F3DBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10360" yWindow="1520" windowWidth="28040" windowHeight="17440" xr2:uid="{34CDE0BD-6A8A-4E44-A287-826F96C9F46C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="22">
   <si>
     <t>date</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A168DAD-D7E7-3142-8DD9-4EBFEE011198}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -995,6 +995,258 @@
         <v>150</v>
       </c>
     </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40">
+        <v>4</v>
+      </c>
+      <c r="D40">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47">
+        <v>5</v>
+      </c>
+      <c r="D47">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53">
+        <v>8</v>
+      </c>
+      <c r="D53">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
